--- a/event_registration_forms/038_scuba_diving_gear_checklist_form--event_registration_forms.xlsx
+++ b/event_registration_forms/038_scuba_diving_gear_checklist_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dive_Comp</t>
+          <t>Dive Comp</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dive_Computer</t>
+          <t>Dive Computer</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Weight_Bag</t>
+          <t>Weight Bag</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weight_Scales</t>
+          <t>Weight Scales</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dive_Light</t>
+          <t>Dive Light</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dive_Bag</t>
+          <t>Dive Bag</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dive_Slate</t>
+          <t>Dive Slate</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dive_Signal_Device</t>
+          <t>Dive Signal Device</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Underwater_Camera</t>
+          <t>Underwater Camera</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Underwater_Lamp</t>
+          <t>Underwater Lamp</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dive_Flag</t>
+          <t>Dive Flag</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Underwater_Videocamera</t>
+          <t>Underwater Videocamera</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dive_Wet_Suit</t>
+          <t>Dive Wet Suit</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dive_Computer</t>
+          <t>Dive Computer</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dive_Computer</t>
+          <t>Dive Computer</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Underwater_Camera</t>
+          <t>Underwater Camera</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Underwater_Lamp</t>
+          <t>Underwater Lamp</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dive_Flag</t>
+          <t>Dive Flag</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dive_Signal_Device</t>
+          <t>Dive Signal Device</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dive_Wet_Suit</t>
+          <t>Dive Wet Suit</t>
         </is>
       </c>
     </row>
